--- a/basedatos_partidas/salida/descompuestos/07.10.01.050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.10.01.050.xlsx
@@ -584,10 +584,10 @@
         <v>0.08</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -610,10 +610,10 @@
         <v>0.08</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="13">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.86</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="14">
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>10.22</v>
+        <v>10.3</v>
       </c>
       <c r="H23" t="n">
         <v>0.1</v>
@@ -814,7 +814,7 @@
       </c>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="5" t="n">
-        <v>10.32</v>
+        <v>10.4</v>
       </c>
     </row>
   </sheetData>
